--- a/artfynd/S 1542-2024 artfynd.xlsx
+++ b/artfynd/S 1542-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490375</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490376</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490379</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1192,6 +1212,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490381</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1322,6 +1347,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490382</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,6 +1482,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490386</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1582,6 +1617,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490390</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1710,6 +1750,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490391</t>
         </is>
       </c>
     </row>
@@ -1815,6 +1860,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490748</t>
         </is>
       </c>
     </row>
@@ -1933,6 +1983,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490387</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2063,6 +2118,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490374</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2193,6 +2253,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490380</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2294,6 +2359,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530976</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2393,6 +2463,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530978</t>
         </is>
       </c>
     </row>
@@ -2500,6 +2575,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490747</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2605,6 +2685,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490749</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2734,6 +2819,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490575</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2853,6 +2943,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98951296</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2972,6 +3067,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99071376</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3091,6 +3191,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106805315</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3210,6 +3315,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98951304</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3333,6 +3443,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100166314</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3456,6 +3571,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98588484</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3575,6 +3695,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98951298</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3694,6 +3819,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99580194</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3813,6 +3943,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98951299</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3932,6 +4067,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106805306</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4051,6 +4191,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99071412</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4170,6 +4315,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98588517</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4289,6 +4439,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98951312</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4408,6 +4563,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98951310</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4527,6 +4687,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99104009</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4646,6 +4811,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100166356</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4747,6 +4917,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530977</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4866,6 +5041,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98951317</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4985,6 +5165,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99104092</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5104,6 +5289,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99712623</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5217,6 +5407,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491027</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5335,6 +5530,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491028</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5448,6 +5648,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491029</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5566,6 +5771,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491030</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5679,6 +5889,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491031</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5792,6 +6007,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491032</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5905,6 +6125,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491033</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6018,6 +6243,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491035</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6141,6 +6371,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491036</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6254,6 +6489,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491037</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6367,6 +6607,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491039</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6480,6 +6725,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491041</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6593,6 +6843,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491042</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6711,6 +6966,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491043</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6824,6 +7084,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491044</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6937,6 +7202,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491045</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7050,6 +7320,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491046</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7173,6 +7448,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491048</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7286,6 +7566,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491050</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7399,6 +7684,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491052</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7512,6 +7802,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491053</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7625,6 +7920,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491054</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7738,6 +8038,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491057</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7851,6 +8156,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491058</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7964,6 +8274,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491060</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8077,6 +8392,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491062</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8190,6 +8510,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491063</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8303,6 +8628,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491064</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8416,6 +8746,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491065</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8517,6 +8852,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530975</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8618,6 +8958,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530979</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8722,6 +9067,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491038</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8826,6 +9176,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491061</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8930,6 +9285,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491047</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9034,8 +9394,87 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>